--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/ba-agile-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/ba-agile-medium.xlsx
@@ -460,7 +460,7 @@
         <v>Yêu cầu chưa đạt DoD không được coi là hoàn thành. Nó phải được đưa lại vào Product Backlog để PO sắp xếp lại độ ưu tiên và không được tính vào Velocity của sprint đó.</v>
       </c>
       <c r="F2" t="str">
-        <v>Chuyển User Story đó về Product Backlog và không tính vào Velocity của Sprint hiện tại — xử lý story dang dở</v>
+        <v>Yêu cầu QA ký biên bản nghiệm thu tạm thời để báo cáo tiến độ đẹp cho khách hàng — gian lận báo cáo</v>
       </c>
       <c r="G2" t="str">
         <v>Vẫn tính là hoàn thành và đưa lên production, sau đó sửa lỗi sau ở Sprint tiếp theo — bàn giao ép buộc</v>
@@ -469,10 +469,10 @@
         <v>Chia đôi Story Point của nó và tính một nửa điểm cho Sprint hiện tại — chia điểm công việc</v>
       </c>
       <c r="I2" t="str">
-        <v>Yêu cầu QA ký biên bản nghiệm thu tạm thời để báo cáo tiến độ đẹp cho khách hàng — gian lận báo cáo</v>
+        <v>Chuyển User Story đó về Product Backlog và không tính vào Velocity của Sprint hiện tại — xử lý story dang dở</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Planning Poker sử dụng dãy số Fibonacci trên các thẻ bài. Các thành viên bỏ phiếu đồng thời để tránh bị ảnh hưởng bởi ý kiến người khác, sau đó thảo luận để đạt được sự đồng thuận.</v>
       </c>
       <c r="F3" t="str">
+        <v>Bốc thăm ngẫu nhiên để chọn ra số điểm cho từng User Story — ước lượng ngẫu nhiên</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Lập trình viên nào xung phong làm task đó sẽ tự quyết định điểm số — ước lượng cá nhân</v>
+      </c>
+      <c r="H3" t="str">
         <v>Đồng thuận tập thể thông qua thảo luận và bỏ phiếu ẩn danh bằng các quân bài Fibonacci — ước lượng đồng thuận</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>Quản lý dự án tự áp đặt điểm số dựa trên kinh nghiệm cá nhân của mình — ước lượng đơn phương</v>
       </c>
-      <c r="H3" t="str">
-        <v>Lập trình viên nào xung phong làm task đó sẽ tự quyết định điểm số — ước lượng cá nhân</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Bốc thăm ngẫu nhiên để chọn ra số điểm cho từng User Story — ước lượng ngẫu nhiên</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Epic là một khối công việc/yêu cầu lớn chưa thể ước lượng chi tiết. Epic cần được phân rã thành các User Story nhỏ hơn, tuân thủ tiêu chuẩn INVEST để vừa vào một Sprint.</v>
       </c>
       <c r="F4" t="str">
+        <v>Epic chỉ dùng cho kiểm thử tự động; còn User Story chỉ dùng cho kiểm thử thủ công — phân chia công cụ</v>
+      </c>
+      <c r="G4" t="str">
         <v>Epic là một yêu cầu lớn, khái quát; được phân rã thành nhiều User Story nhỏ có thể hoàn thành trong một Sprint — phân cấp yêu cầu</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Epic là tài liệu đặc tả kỹ thuật; còn User Story là mã nguồn lập trình thực tế — phân chia kỹ thuật</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>Epic do khách hàng viết; còn User Story do lập trình viên tự viết khi code — phân chia tác giả</v>
       </c>
-      <c r="I4" t="str">
-        <v>Epic chỉ dùng cho kiểm thử tự động; còn User Story chỉ dùng cho kiểm thử thủ công — phân chia công cụ</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -559,13 +559,13 @@
         <v>Tổng số Story Points của các User Story đạt DoD mà team hoàn thành được trong một Sprint — năng suất trung bình</v>
       </c>
       <c r="G5" t="str">
-        <v>Tốc độ tải trang và phản hồi của hệ thống phần mềm trên máy chủ — tốc độ hệ thống</v>
+        <v>Số lượng tính năng mới được PO thêm vào Product Backlog trong một tuần — tốc độ thêm yêu cầu</v>
       </c>
       <c r="H5" t="str">
         <v>Tổng số giờ mà các lập trình viên đã OT (làm thêm giờ) trong Sprint đó — giờ làm việc</v>
       </c>
       <c r="I5" t="str">
-        <v>Số lượng tính năng mới được PO thêm vào Product Backlog trong một tuần — tốc độ thêm yêu cầu</v>
+        <v>Tốc độ tải trang và phản hồi của hệ thống phần mềm trên máy chủ — tốc độ hệ thống</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -591,13 +591,13 @@
         <v>Đề xuất dành nửa ngày họp Backlog Refinement trước khi chốt scope Sprint để tránh rủi ro ước lượng sai — làm mịn backlog</v>
       </c>
       <c r="G6" t="str">
+        <v>Hủy bỏ toàn bộ Sprint hiện tại và cho team nghỉ ngơi cho đến khi tài liệu sẵn sàng — trì hoãn dự án</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Yêu cầu Scrum Master tự viết Acceptance Criteria thay cho BA và PO — đùn đẩy công việc</v>
+      </c>
+      <c r="I6" t="str">
         <v>Ép buộc team ước lượng đại khái và tiến hành làm, có gì mập mờ sẽ giải thích sau khi code — chấp nhận rủi ro</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Hủy bỏ toàn bộ Sprint hiện tại và cho team nghỉ ngơi cho đến khi tài liệu sẵn sàng — trì hoãn dự án</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Yêu cầu Scrum Master tự viết Acceptance Criteria thay cho BA và PO — đùn đẩy công việc</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -620,7 +620,7 @@
         <v>Trong INVEST, "V" là Valuable. Mọi câu chuyện người dùng phải đem lại giá trị hữu ích cho khách hàng hoặc người dùng cuối, không viết các story thuần kỹ thuật không có giá trị nghiệp vụ.</v>
       </c>
       <c r="F7" t="str">
-        <v>Valuable — Mỗi User Story được viết ra phải mang lại giá trị thực tế cho người dùng hoặc doanh nghiệp — giá trị nghiệp vụ</v>
+        <v>Visual — Giao diện của Story phải được vẽ đẹp mắt bằng các công cụ thiết kế chuyên nghiệp — tính trực quan</v>
       </c>
       <c r="G7" t="str">
         <v>Verifiable — Story phải được cài đặt thành công trên môi trường của khách hàng — xác thực cài đặt</v>
@@ -629,10 +629,10 @@
         <v>Variable — Nội dung yêu cầu có thể thay đổi liên tục trong suốt quá trình code — tính biến động</v>
       </c>
       <c r="I7" t="str">
-        <v>Visual — Giao diện của Story phải được vẽ đẹp mắt bằng các công cụ thiết kế chuyên nghiệp — tính trực quan</v>
+        <v>Valuable — Mỗi User Story được viết ra phải mang lại giá trị thực tế cho người dùng hoặc doanh nghiệp — giá trị nghiệp vụ</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Backlog Refinement là hoạt động liên tục giúp chuẩn bị sẵn sàng các backlog item cho sprint tiếp theo bằng cách làm rõ chi tiết, viết AC và ước lượng sơ bộ.</v>
       </c>
       <c r="F8" t="str">
-        <v>Diễn ra trong suốt Sprint để PO, BA và team thảo luận, làm rõ và ước lượng trước các story cho các sprint sau — chuẩn bị yêu cầu</v>
+        <v>Diễn ra ngay trên môi trường Production để vá các lỗi bảo mật khẩn cấp — vá lỗi hệ thống</v>
       </c>
       <c r="G8" t="str">
         <v>Diễn ra vào ngày cuối cùng của Sprint để chấm điểm hiệu suất của từng lập trình viên — đánh giá nhân sự</v>
       </c>
       <c r="H8" t="str">
-        <v>Diễn ra ngay trên môi trường Production để vá các lỗi bảo mật khẩn cấp — vá lỗi hệ thống</v>
+        <v>Diễn ra trước khi ký hợp đồng dự án để chốt tổng chi phí với khách hàng — báo giá dự án</v>
       </c>
       <c r="I8" t="str">
-        <v>Diễn ra trước khi ký hợp đồng dự án để chốt tổng chi phí với khách hàng — báo giá dự án</v>
+        <v>Diễn ra trong suốt Sprint để PO, BA và team thảo luận, làm rõ và ước lượng trước các story cho các sprint sau — chuẩn bị yêu cầu</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -687,13 +687,13 @@
         <v>Vi phạm tiêu chí Testable (Không thể kiểm thử) vì từ "chạy nhanh hơn" quá mơ hồ, không có chỉ số đo lường — thiếu tính định lượng</v>
       </c>
       <c r="G9" t="str">
-        <v>Vi phạm tiêu chí Independent vì quản trị viên không thể thực hiện các hành động độc lập — phụ thuộc vai trò</v>
+        <v>Vi phạm tiêu chí Valuable vì việc tiết kiệm thời gian không mang lại giá trị cho doanh nghiệp — giá trị thấp</v>
       </c>
       <c r="H9" t="str">
         <v>Vi phạm tiêu chí Small vì đây là một yêu cầu quá nhỏ không cần viết thành User Story — kích thước quá nhỏ</v>
       </c>
       <c r="I9" t="str">
-        <v>Vi phạm tiêu chí Valuable vì việc tiết kiệm thời gian không mang lại giá trị cho doanh nghiệp — giá trị thấp</v>
+        <v>Vi phạm tiêu chí Independent vì quản trị viên không thể thực hiện các hành động độc lập — phụ thuộc vai trò</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -716,19 +716,19 @@
         <v>Sprint Review là buổi họp cuối Sprint để team trình bày kết quả công việc đã hoàn thành đạt DoD cho khách hàng/stakeholder xem và lấy ý kiến phản hồi.</v>
       </c>
       <c r="F10" t="str">
-        <v>Trình bày phần tăng trưởng sản phẩm (Increment) đã hoàn thành cho các bên liên quan và nhận phản hồi đóng góp — demo và nhận feedback</v>
+        <v>Đứng ra phân tích lỗi và chỉ trích các thành viên làm phát sinh bug trong sprint — tìm người chịu trách nhiệm</v>
       </c>
       <c r="G10" t="str">
         <v>Thực hiện viết code bổ sung cho các tính năng chưa kịp hoàn thành trong sprint — chạy nước rút code</v>
       </c>
       <c r="H10" t="str">
-        <v>Đứng ra phân tích lỗi và chỉ trích các thành viên làm phát sinh bug trong sprint — tìm người chịu trách nhiệm</v>
+        <v>Trình bày phần tăng trưởng sản phẩm (Increment) đã hoàn thành cho các bên liên quan và nhận phản hồi đóng góp — demo và nhận feedback</v>
       </c>
       <c r="I10" t="str">
         <v>Lên danh sách phân chia công việc chi tiết cho sprint tiếp theo — lập kế hoạch tương lai</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Business Rules (như quy định tuổi mua hàng &gt; 18) tồn tại độc lập với phần mềm. Acceptance Criteria là các kịch bản cụ thể để kiểm tra xem tính năng phần mềm có đáp ứng đúng quy tắc đó hay không.</v>
       </c>
       <c r="F11" t="str">
+        <v>Quy tắc nghiệp vụ luôn thay đổi hàng ngày; Tiêu chí nghiệm thu không bao giờ được phép thay đổi — tính ổn định</v>
+      </c>
+      <c r="G11" t="str">
         <v>Quy tắc nghiệp vụ là ràng buộc chung của tổ chức; Tiêu chí nghiệm thu là các điều kiện cụ thể để nghiệm thu một story riêng lẻ — phạm vi áp dụng</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Quy tắc nghiệp vụ do Dev tự quy định; Tiêu chí nghiệm thu do khách hàng bắt buộc phải viết — chủ thể viết</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <v>Quy tắc nghiệp vụ chỉ áp dụng cho tài liệu Word; Tiêu chí nghiệm thu chỉ viết trực tiếp trong code — hình thức tài liệu</v>
       </c>
-      <c r="I11" t="str">
-        <v>Quy tắc nghiệp vụ luôn thay đổi hàng ngày; Tiêu chí nghiệm thu không bao giờ được phép thay đổi — tính ổn định</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
